--- a/data/film_bilgi_sablonu.xlsx
+++ b/data/film_bilgi_sablonu.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\korhan.ors\Desktop\Flashdisk Korhan\GitHub\arsiv\Projeler\Değişik Sorgular\Film Bilgisi Çekme\film-bilgi-sistemi\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\korhan.ors\Desktop\Flashdisk Korhan\GitHub\arsiv\Projeler\film-bilgi-sistemi\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6801BF32-EF03-41AE-9235-38F5FE0E075E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6891DC6-096E-469A-9606-99F49C335EAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Filmler" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>Türkçe Film Adı</t>
   </si>
@@ -56,13 +56,28 @@
   </si>
   <si>
     <t>The godfather</t>
+  </si>
+  <si>
+    <t>Kara Şövalye</t>
+  </si>
+  <si>
+    <t>Dövüş Kulübü</t>
+  </si>
+  <si>
+    <t>12 Öfkeli Adam</t>
+  </si>
+  <si>
+    <t>Yüzüklerin Efendisi: Yüzük Kardeşliği</t>
+  </si>
+  <si>
+    <t>12 maymun</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -74,6 +89,16 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="162"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -98,10 +123,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -109,8 +135,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Köprü" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -411,7 +441,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -473,7 +503,9 @@
       <c r="J2" s="2"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" s="2"/>
+      <c r="A3" s="3" t="s">
+        <v>11</v>
+      </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -485,7 +517,9 @@
       <c r="J3" s="2"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" s="2"/>
+      <c r="A4" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -497,7 +531,9 @@
       <c r="J4" s="2"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" s="2"/>
+      <c r="A5" s="3" t="s">
+        <v>13</v>
+      </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
@@ -509,7 +545,9 @@
       <c r="J5" s="2"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="2"/>
+      <c r="A6" s="3" t="s">
+        <v>14</v>
+      </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
@@ -520,8 +558,19 @@
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
     </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:J1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <hyperlinks>
+    <hyperlink ref="A3" r:id="rId1" display="https://www.imdb.com/title/tt0468569/?ref_=ls_t_2" xr:uid="{16E337A5-76A2-4643-9C58-3B4E0F8CA780}"/>
+    <hyperlink ref="A4" r:id="rId2" display="https://www.imdb.com/title/tt0137523/?ref_=ls_t_5" xr:uid="{E4E911F9-F3E2-471D-91D2-F48A79E95284}"/>
+    <hyperlink ref="A5" r:id="rId3" display="https://www.imdb.com/title/tt0050083/?ref_=ls_t_9" xr:uid="{7A8CBD85-CFC1-41E0-8F88-04285BC17174}"/>
+    <hyperlink ref="A6" r:id="rId4" display="https://www.imdb.com/title/tt0120737/?ref_=ls_t_10" xr:uid="{2CBF4F34-EFCF-4972-A740-18C0E7B40BF3}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/film_bilgi_sablonu.xlsx
+++ b/data/film_bilgi_sablonu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\korhan.ors\Desktop\Flashdisk Korhan\GitHub\arsiv\Projeler\film-bilgi-sistemi\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6891DC6-096E-469A-9606-99F49C335EAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEA10955-E22D-4F16-8C8F-ACD256C81AD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>Türkçe Film Adı</t>
   </si>
@@ -71,6 +71,9 @@
   </si>
   <si>
     <t>12 maymun</t>
+  </si>
+  <si>
+    <t>The rookie</t>
   </si>
 </sst>
 </file>
@@ -441,7 +444,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -563,6 +566,11 @@
         <v>15</v>
       </c>
     </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>16</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:J1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <hyperlinks>
